--- a/output/2026-10-07_00_Serbia_Grad_Beograd_ATEX_Equipment-Services.xlsx
+++ b/output/2026-10-07_00_Serbia_Grad_Beograd_ATEX_Equipment-Services.xlsx
@@ -474,7 +474,6 @@
           <t>Sobel d.o.o.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Grad Beograd (Vozdovac / Sumice)</t>
@@ -490,7 +489,6 @@
           <t>011/308-7507</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Azienda reale confermata: Ustanicka 125-I, Sumice, 11000 Beograd. Rappresenta in Serbia circa 10 brand tedeschi del settore elettrotecnico, tra cui WERMA (dispositivi di segnalazione ottica/acustica), citata come contatto ufficiale WERMA per la Serbia in fonte giornalistica specializzata (magazinmehatronika.com) e in directory locali (planplus.rs). Distributore indipendente multi-brand, non filiale di un singolo produttore. NON è stato possibile confermare da fonti indipendenti la presenza specifica della linea 'Ex' certificata ATEX (il claim è presente solo nella lista grezza fornita, non riscontrato nelle fonti consultate). Sito web ed email non reperiti: lasciati vuoti.</t>
@@ -508,7 +506,6 @@
           <t>N Trade d.o.o.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Grad Beograd</t>
@@ -519,8 +516,6 @@
           <t>ATEX Equipment/Services - componenti sicurezza intrinseca / protezione da esplosione (ASCO, AVENTICS, TOPWORX, GEORGIN)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Azienda reale confermata tramite directory B2B di settore (automa.net - business directory Serbia, service provider ASCO/Numatics/Joucomatic). Fondata nel 1994, distributore autorizzato indipendente multi-brand per Serbia, Bosnia-Erzegovina, Montenegro, Macedonia del Nord e Albania di componentistica industriale (valvole solenoidi e pneumatiche ASCO, pneumatica AVENTICS, controllo valvole TOPWORX, pressostati/termostati GEORGIN) incluse soluzioni per sicurezza intrinseca in zone Ex - coerente col target ATEX. Non è un produttore né una filiale diretta di uno dei brand rappresentati. NON è stato possibile reperire sito web ufficiale, telefono o indirizzo esatto da fonti verificabili nella ricerca effettuata: campi lasciati vuoti.</t>
@@ -528,7 +523,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
